--- a/data/satisfaction_detail/2026/1-8月/酒店参会客户.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/酒店参会客户.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.840822324791766</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.91</v>
+        <v>9.956482041487613</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.93</v>
+        <v>9.982842591118892</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99264682476524</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.9</v>
+        <v>9.95032258064516</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.912987426388668</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.91</v>
+        <v>9.979166003501513</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9.57</v>
+        <v>9.655467664067061</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>9.82</v>
+        <v>9.895999257255028</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.67</v>
+        <v>9.75125205581198</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.85</v>
+        <v>9.954655419385645</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.32700090190461</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.69541514138681</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.41</v>
+        <v>9.490570852565122</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.877692185261818</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.57</v>
+        <v>9.692753461722107</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.957106477797232</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.67</v>
+        <v>9.802018674730755</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.882086582842591</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.4</v>
+        <v>9.305039300668478</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.92363916844193</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9.81</v>
+        <v>9.858393018197251</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.83</v>
+        <v>9.899098095389677</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.76</v>
+        <v>9.881792137513928</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.988970237147859</v>
       </c>
     </row>
     <row r="18">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9.710000000000001</v>
+        <v>9.848517162714202</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9.859999999999999</v>
+        <v>9.962580508249774</v>
       </c>
     </row>
     <row r="19">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.24</v>
+        <v>9.629973821989529</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.889136125654451</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.59</v>
+        <v>9.654109947643979</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.933385689354276</v>
       </c>
     </row>
     <row r="21">
